--- a/PreC2D/Data_obs.xlsx
+++ b/PreC2D/Data_obs.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R-4.2.1\Cerema\PreC2D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R-4.4.2\Cerema\PreC2D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AED869-89F9-49B7-B12F-26BDC8CDBD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEDA18F-6736-4C9A-8B20-B6BF61F5B989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="17520" xr2:uid="{B5172189-CE5C-46CB-9876-512FA5B14147}"/>
+    <workbookView xWindow="3410" yWindow="1310" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -29,16 +26,55 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+  <si>
+    <t>Cas</t>
+  </si>
+  <si>
+    <t>Localisation</t>
+  </si>
+  <si>
+    <t>Evenements</t>
+  </si>
   <si>
     <t xml:space="preserve">Type </t>
   </si>
   <si>
+    <t>Format_date</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Col_Debit</t>
+  </si>
+  <si>
+    <t>Col_Hauteur</t>
+  </si>
+  <si>
+    <t>Col_Cote</t>
+  </si>
+  <si>
+    <t>Colonne_type</t>
+  </si>
+  <si>
+    <t>Nom_Debit</t>
+  </si>
+  <si>
+    <t>Nom_Hauteur</t>
+  </si>
+  <si>
+    <t>Nom_Cote</t>
+  </si>
+  <si>
     <t>unit_debit</t>
   </si>
   <si>
@@ -51,114 +87,78 @@
     <t>Noms</t>
   </si>
   <si>
+    <t>nom_dossier</t>
+  </si>
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>EPSG</t>
+  </si>
+  <si>
+    <t>ext</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>shp</t>
+  </si>
+  <si>
+    <t>nom_post</t>
+  </si>
+  <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
+    <t>Fiona</t>
+  </si>
+  <si>
+    <t>CVH</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> %d/%m/%Y %H:%M</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
     <t>dossiers</t>
   </si>
   <si>
-    <t>nom_dossier</t>
-  </si>
-  <si>
-    <t>Cas</t>
-  </si>
-  <si>
-    <t>Localisation</t>
-  </si>
-  <si>
-    <t>Guadeloupe</t>
-  </si>
-  <si>
-    <t>CVH</t>
-  </si>
-  <si>
-    <t>Colonne_type</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Skip</t>
-  </si>
-  <si>
-    <t>Fiona</t>
-  </si>
-  <si>
-    <t>Format_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> %d/%m/%Y %H:%M</t>
-  </si>
-  <si>
-    <t>EPSG</t>
+    <t>D:/Cartino2D/Guadeloupe/_SectionsControles/CVH_FIONA</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>csv</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>D:/Cartino2D/Guadeloupe/_SectionsControles/SectControl_5490.shp</t>
+  </si>
+  <si>
+    <t>D:/Cartino2D/Guadeloupe/_SectionsControles/FIONA3_03m</t>
   </si>
   <si>
     <t>Nimes</t>
   </si>
   <si>
-    <t>Evenements</t>
-  </si>
-  <si>
     <t>PAPI3</t>
   </si>
   <si>
-    <t>ext</t>
-  </si>
-  <si>
-    <t>csv</t>
-  </si>
-  <si>
-    <t>Col_Debit</t>
-  </si>
-  <si>
-    <t>Nom_Debit</t>
-  </si>
-  <si>
-    <t>Col_Hauteur</t>
-  </si>
-  <si>
-    <t>Col_Cote</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>Nom_Hauteur</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Nom_Cote</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>;</t>
-  </si>
-  <si>
-    <t>shp</t>
-  </si>
-  <si>
-    <t>D:/Cartino2D/Guadeloupe/_SectionsControles/SectControl_5490.shp</t>
-  </si>
-  <si>
-    <t>D:/Cartino2D/Guadeloupe/_SectionsControles/CVH_FIONA</t>
-  </si>
-  <si>
-    <t>header</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>nom_post</t>
-  </si>
-  <si>
-    <t>D:/Cartino2D/Guadeloupe/_SectionsControles/FIONA3_03m</t>
-  </si>
-  <si>
     <t xml:space="preserve"> %d/%m/%Y  %H:%M</t>
   </si>
   <si>
@@ -171,37 +171,66 @@
     <t>MTP</t>
   </si>
   <si>
+    <t>%Y-%m-%d %H:%M:%S</t>
+  </si>
+  <si>
     <t>Mesure niveau</t>
   </si>
   <si>
+    <t>file</t>
+  </si>
+  <si>
     <t>C:/Cartino2D/France/_SectionsControles/MTP</t>
   </si>
   <si>
+    <t>,</t>
+  </si>
+  <si>
     <t>C:/Cartino2D/France/_SectionsControles/SectControl_PPRiMtpCLL_20220610.shp</t>
   </si>
   <si>
     <t>C:/Cartino2D/France/_SectionsControles/MTPREF</t>
   </si>
   <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>%Y-%m-%d %H:%M:%S</t>
-  </si>
-  <si>
-    <t>file</t>
+    <t>Reunion</t>
+  </si>
+  <si>
+    <t>GARANCE</t>
+  </si>
+  <si>
+    <t>Cadiere</t>
+  </si>
+  <si>
+    <t>2015_09</t>
+  </si>
+  <si>
+    <t>SMART</t>
+  </si>
+  <si>
+    <t>%Y-%m-%d-T%H:%M:%S</t>
+  </si>
+  <si>
+    <t>C:\Cartino2D\France\_SectionsControles\MAMP\Données_smart_cadière_21sept25</t>
+  </si>
+  <si>
+    <t>C:\Cartino2D\France\_SectionsControles\MAMP\Données_smart_cadière_21sept25\stations_smart_cadière.gpkg</t>
+  </si>
+  <si>
+    <t>Hauteur d'eau</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -209,7 +238,6 @@
       <sz val="14"/>
       <color theme="3" tint="0.249977111117893"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -233,10 +261,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -297,108 +326,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Display"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -406,7 +341,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -432,7 +367,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -484,16 +419,28 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -509,7 +456,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -541,7 +488,7 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -561,32 +508,27 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5CE80E5-9A2B-41B6-AB05-6DBCBFF0C0ED}">
-  <dimension ref="A1:Z4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.375" customWidth="1"/>
-    <col min="6" max="6" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="53" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="53" customWidth="1"/>
     <col min="25" max="25" width="69.75" bestFit="1" customWidth="1"/>
@@ -594,82 +536,82 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
@@ -677,16 +619,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -701,10 +643,10 @@
         <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N2">
         <f>1/1000</f>
@@ -715,13 +657,13 @@
         <v>1E-3</v>
       </c>
       <c r="Q2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -730,19 +672,19 @@
         <v>5490</v>
       </c>
       <c r="V2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="W2">
         <v>4</v>
       </c>
       <c r="X2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Z2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -750,13 +692,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>41</v>
@@ -783,10 +725,10 @@
         <v>2154</v>
       </c>
       <c r="V3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="X3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -803,7 +745,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -824,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -836,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -851,7 +793,7 @@
         <v>2154</v>
       </c>
       <c r="V4" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="W4">
         <v>-2</v>
@@ -860,13 +802,81 @@
         <v>49</v>
       </c>
       <c r="Y4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="M6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6">
+        <v>4326</v>
+      </c>
+      <c r="V6" t="s">
+        <v>35</v>
+      </c>
+      <c r="X6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>